--- a/aux1.xlsx
+++ b/aux1.xlsx
@@ -351,18 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>s2_08a</t>
+          <t>s2_08a.x</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>po</t>
         </is>
       </c>
     </row>
@@ -373,7 +383,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.3714387376495069</v>
+        <v>0.05500369271757346</v>
+      </c>
+      <c r="C2">
+        <v>0.3404525613425052</v>
+      </c>
+      <c r="D2">
+        <v>0.6045437459399213</v>
       </c>
     </row>
     <row r="3">
@@ -383,17 +399,29 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.3237971574834897</v>
+        <v>0.1153536959183708</v>
+      </c>
+      <c r="C3">
+        <v>0.3592881845621523</v>
+      </c>
+      <c r="D3">
+        <v>0.525358119519477</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Consultó e hizo gestiones por INTERNET o a través de redes sociales</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.1984915332334349</v>
+        <v>0.0980089357864543</v>
+      </c>
+      <c r="C4">
+        <v>0.3340217379383095</v>
+      </c>
+      <c r="D4">
+        <v>0.5679693262752362</v>
       </c>
     </row>
     <row r="5">
@@ -403,17 +431,29 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.05700174025057313</v>
+        <v>0.5243984618874367</v>
+      </c>
+      <c r="C5">
+        <v>0.09522220353760766</v>
+      </c>
+      <c r="D5">
+        <v>0.3803793345749557</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Consultó e hizo gestiones por INTERNET o a través de redes sociales</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.04927083138299544</v>
+        <v>0.06600897157777109</v>
+      </c>
+      <c r="C6">
+        <v>0.3619819458268496</v>
+      </c>
+      <c r="D6">
+        <v>0.5720090825953792</v>
       </c>
     </row>
   </sheetData>
